--- a/stories/arbres/TREE-DIF-019.xlsx
+++ b/stories/arbres/TREE-DIF-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec maman, au marché. Sara a envie de jouer. maman est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara écoute maman. Sara entend les mots : énergie, pas une faute, jouer ou attendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-019.xlsx
+++ b/stories/arbres/TREE-DIF-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec maman, au marché. Sara a envie de jouer. maman est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara écoute maman. Sara entend les mots : énergie, pas une faute, jouer ou attendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Sara rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Sara rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Sara rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Sara rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Sara rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Sara rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Sara rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara respire. Sara retient : énergie, pas une faute, jouer ou attendre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Sara rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Sara rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Sara rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Sara rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara répète tout bas : énergie, pas une faute, jouer ou attendre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Sara rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Sara rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Sara rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Sara a entendu : énergie, pas une faute, jouer ou attendre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-019.xlsx
+++ b/stories/arbres/TREE-DIF-019.xlsx
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Sous les pieds, le sable chuchote encore. Un trou rond reste au milieu du bac.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Sous les pieds, le sable chuchote encore. Un trou rond reste au milieu du bac.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Sous les pieds, le sable chuchote encore. Un trou rond reste au milieu du bac.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Sous les pieds, le sable chuchote encore. Un trou rond reste au milieu du bac.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
 enfant-f|Tu l'avais attaché, pile.
 copain|Il n'est pas parti.
 papa|Vous avez demandé, et ça a tenu.
-maman|Le vert de la feuille sent encore.
+maman|La pêche sent encore le soleil.
 narrateur|Trois bouches, un même sucré.
 narrateur|Le doudou reprend le sac, tout doux.
 narrateur|Sous les pieds, le sable chuchote encore.
@@ -11435,12 +11435,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Un petit toc dort encore dans le métal. Vide et chaud, le toboggan se tait.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Un petit toc dort encore dans le métal. Vide et chaud, le toboggan se tait.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Un petit toc dort encore dans le métal. Vide et chaud, le toboggan se tait.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Un petit toc dort encore dans le métal. Vide et chaud, le toboggan se tait.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -11579,7 +11579,7 @@
 enfant-f|Tu l'avais attaché, pile.
 copain|Il n'est pas parti.
 papa|Vous avez demandé, et ça a tenu.
-maman|Le vert de la feuille sent encore.
+maman|La pêche sent encore le soleil.
 narrateur|Trois bouches, un même sucré.
 narrateur|Le doudou reprend le sac, tout doux.
 narrateur|Un petit toc dort encore dans le métal.
@@ -16447,12 +16447,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Puis la chaîne se tait, tout doux. Plus aucun cri sur la chaîne.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Puis la chaîne se tait, tout doux. Plus aucun cri sur la chaîne.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. Le vert de la feuille sent encore. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Puis la chaîne se tait, tout doux. Plus aucun cri sur la chaîne.</t>
+          <t>Maman détache le doudou, plus tard. Tu l'avais attaché, pile. Il n'est pas parti. Vous avez demandé, et ça a tenu. La pêche sent encore le soleil. Trois bouches, un même sucré. Le doudou reprend le sac, tout doux. Puis la chaîne se tait, tout doux. Plus aucun cri sur la chaîne.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16591,7 +16591,7 @@
 enfant-f|Tu l'avais attaché, pile.
 copain|Il n'est pas parti.
 papa|Vous avez demandé, et ça a tenu.
-maman|Le vert de la feuille sent encore.
+maman|La pêche sent encore le soleil.
 narrateur|Trois bouches, un même sucré.
 narrateur|Le doudou reprend le sac, tout doux.
 narrateur|Puis la chaîne se tait, tout doux.
@@ -16616,7 +16616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16715,6 +16715,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
